--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,342 +899,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>602883767942</t>
+          <t> </t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>24</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>7908305634063</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BOBOBINA  PULSO MHX YES125 2005 A 2011/ INTRUDER125 2002 A 2016/ KATANA125 1996 A 1996</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>25</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>7908305618681</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BOBOBINA  PULSO MHX CBX150 1990 A 1993/ CBX200 1994 A 2001/ BROS NXR150 1990 A 1993/XR200 1994 A 2002</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>26</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>7908305634186</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BOBOBINA  PULSO MHX JET50 2014 A 2020/ HYPE50 2010 A 2014</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>27</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>7908305634100</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>BOBINA PULSO MHX FAZER250 2006 A 2019/ LANDER250 2007 A 2019/ TENERE 2011 A 2019</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>28</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7908305635152</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO MHX YBR125K 2000 A 2001</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>29</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7908305602505</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO MHX BOBINA IGNICAOZ100 DREAM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>30</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7908305634407</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO MHX CB300R 2010 A 2015/ XRE300 2010 A 2018/ TWISTER250 2001 A 2008/ TORNADO250 2001 A 2008</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7908305634391</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO MHX FAZER150 ED 2014 A 2015/ FACTOR150 2016 A 2018/ XTZ CROSSER 2014 A 2018</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>32</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7899468071010</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO JECPRO CG FAN TITAN150 2004/ BROS NXR150 2006</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>33</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>751320983534</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO IRON YBR 2000 A 2001 182327</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>34</v>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO MAGNETRON CG125</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>35</v>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>BOBINA  PULSO MAGNETRON CG TITAN FAN 2003 A 2004</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>38</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>7898485612213</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BOBINA  LUZ MAGNETRON BOBINA IGNICAOZ DREAM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>39</v>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>BOBINA  LUZ MAGNETRON CG125</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,7 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -753,11 +692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -778,7 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -795,7 +728,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -816,11 +748,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -841,11 +768,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -866,11 +788,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -891,7 +808,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -904,7 +820,6 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
